--- a/sum.var_AMR_ville_FQ_R.xlsx
+++ b/sum.var_AMR_ville_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -26,9 +26,6 @@
     <t xml:space="preserve">log_AMC_EHPAD_FQ</t>
   </si>
   <si>
-    <t xml:space="preserve">log_AMC_EHPAD_aminoglycosides</t>
-  </si>
-  <si>
     <t xml:space="preserve">log_AMC_EHPAD_macrolides</t>
   </si>
   <si>
@@ -56,9 +53,6 @@
     <t xml:space="preserve">log_AMC_ville_FQ</t>
   </si>
   <si>
-    <t xml:space="preserve">log_AMC_ville_aminoglycosides</t>
-  </si>
-  <si>
     <t xml:space="preserve">log_AMC_ville_macrolides</t>
   </si>
   <si>
@@ -83,6 +77,93 @@
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
   </si>
   <si>
+    <t xml:space="preserve">AMR_animaux_compagnie_C3G_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_compagnie_FQ_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_C3G_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_FQ_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_amoxi_clav_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ville_FQ_R.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veto_by_AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veto_by_CV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veto_by_carni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prop_veto_50plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chevaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chiens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_SAU_bovine_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_bovine_all</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_bovins_adultes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_porcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_veaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_volailles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ville_FQ_R.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_NO2_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_O3_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM10_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM25_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resid_FQ_eau_naiades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dju_refroi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_i033b_part_class_5_eau_sup_pes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_ville_FQ_R.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">EQI_st</t>
   </si>
   <si>
@@ -98,18 +179,6 @@
     <t xml:space="preserve">unemployement_pourc</t>
   </si>
   <si>
-    <t xml:space="preserve">veto_by_AC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">veto_by_CV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">veto_by_carni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prop_veto_50plus</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL_medG</t>
   </si>
   <si>
@@ -119,15 +188,6 @@
     <t xml:space="preserve">prop_tabagisme</t>
   </si>
   <si>
-    <t xml:space="preserve">tx_possession_chats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_possession_chevaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_possession_chiens</t>
-  </si>
-  <si>
     <t xml:space="preserve">pop_14_moins_prop</t>
   </si>
   <si>
@@ -135,48 +195,6 @@
   </si>
   <si>
     <t xml:space="preserve">log_pop_density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_NO2_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_O3_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM10_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM25_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resid_FQ_eau_naiades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dju_refroi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_i033b_part_class_5_eau_sup_pes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_SAU_bovine_all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_bovine_all</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_bovins_adultes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_livestock_tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_porcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_veaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_volailles</t>
   </si>
   <si>
     <t xml:space="preserve">Auvergne-Rhone-Alpes</t>
@@ -707,2009 +725,2243 @@
       <c r="BC1" t="s">
         <v>54</v>
       </c>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00566441877541788</v>
+        <v>0.00772960052286772</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0159362514179735</v>
+        <v>-0.0332116974675727</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0117364128434542</v>
+        <v>0.00673395387442586</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.00329269762876311</v>
+        <v>-0.0236791454821986</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.113923085322817</v>
+        <v>-0.0757500947291418</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0305930022316977</v>
+        <v>-0.102978962370727</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0748896455239369</v>
+        <v>-0.0519636488636131</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0223029694271609</v>
+        <v>0.10036063159044</v>
       </c>
       <c r="J2" t="n">
-        <v>0.135967174990009</v>
+        <v>0.0335610808107989</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.068079411657985</v>
+        <v>0.045746548313324</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0643729870271022</v>
+        <v>-0.136759865392762</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.137955780811288</v>
+        <v>-0.0501690072424326</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0562017730346469</v>
+        <v>-0.119218369487267</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000616453193615034</v>
+        <v>-0.0899670434204568</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.170409014497898</v>
+        <v>-0.0729740524328948</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0982233238516458</v>
+        <v>-0.0500340516551097</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.0807801325156192</v>
+        <v>-0.11340677064681</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.019848019280109</v>
+        <v>-0.0580919365243204</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.127725237087184</v>
+        <v>0.037870926705233</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0229034306103123</v>
+        <v>-0.114851315499916</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0564549760587912</v>
+        <v>-0.00704050577408892</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.128275686442433</v>
+        <v>-0.00588658969639042</v>
       </c>
       <c r="X2" t="n">
-        <v>0.018221100465612</v>
+        <v>-0.0057397080210425</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0298892265635627</v>
+        <v>-0.0117322731793835</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0523382592608486</v>
+        <v>-0.0332588684908322</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0135368857864785</v>
+        <v>0.00772960052286772</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.0015947979899766</v>
+        <v>0.154001140422901</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.214439791310213</v>
+        <v>0.0582695830019245</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.184578472026145</v>
+        <v>0.160323399740883</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.22210521248179</v>
+        <v>-0.0133806984731499</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.0118072935270061</v>
+        <v>-12.3303494649166</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.135087381592012</v>
+        <v>-4.38486917941033</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.14932481178154</v>
+        <v>-18.8678731402826</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.000664937754355797</v>
+        <v>0.130610908822835</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-13.28195333135</v>
+        <v>0.375555392934203</v>
       </c>
       <c r="AK2" t="n">
-        <v>-4.59065705019798</v>
+        <v>0.357498405731887</v>
       </c>
       <c r="AL2" t="n">
-        <v>-16.6091167444359</v>
+        <v>0.152621661124171</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0066486533806974</v>
+        <v>-0.346688833462624</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.00183642445924789</v>
+        <v>0.235349613528001</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.0653182165913211</v>
+        <v>-0.209548982113039</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.26277958210213</v>
+        <v>0.00772960052286772</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.54771264744609</v>
+        <v>2.46131616730103</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.315225740692691</v>
+        <v>-2.19227167052624</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.521012349984676</v>
+        <v>-0.14689466098425</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0057092416355039</v>
+        <v>0.464358721866095</v>
       </c>
       <c r="AU2" t="n">
-        <v>12.8102312449722</v>
+        <v>0.0193427664342699</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.00135038279508451</v>
+        <v>11.0218902694913</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.129098313230902</v>
+        <v>-0.0193912798365033</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.387290759845462</v>
+        <v>0.00772960052286772</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.363982891665085</v>
+        <v>-0.0976156339794002</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.166015466368067</v>
+        <v>0.0231009862779099</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.31505429773053</v>
+        <v>0.0711842396775379</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.263182436604977</v>
+        <v>0.0133997267485429</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0.201079131308133</v>
+        <v>-0.0116735390973381</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.23814057256977</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.102157056829545</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.0148335863570865</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.00535566593062078</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.00172099403356767</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-0.073997723673461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.0168070305263355</v>
+        <v>-0.0221341414530939</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0349668949988311</v>
+        <v>-0.0269866252159834</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0544524085129533</v>
+        <v>-0.0626853491315937</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0193524897792711</v>
+        <v>0.0667609974418947</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0021289679117607</v>
+        <v>0.00896430553400415</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.00414082158915148</v>
+        <v>0.0402110528836817</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0374100357657006</v>
+        <v>0.0110822982171971</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00260192400074352</v>
+        <v>0.0352159793973484</v>
       </c>
       <c r="J3" t="n">
-        <v>0.100635212457292</v>
+        <v>-0.0975259174762126</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0493082408835491</v>
+        <v>0.0890607105496024</v>
       </c>
       <c r="L3" t="n">
-        <v>0.149214914344293</v>
+        <v>0.0674197177529147</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0361975175949806</v>
+        <v>-0.0113250537682787</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.00151287876461758</v>
+        <v>0.0302138660849762</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0029954449329773</v>
+        <v>-0.0164060544761927</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00106445752264794</v>
+        <v>0.0138953877725435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0221498750873363</v>
+        <v>0.0264843564568429</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0107022843233079</v>
+        <v>0.0155037622756563</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0494459691465362</v>
+        <v>0.0187351769509707</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.000707302474764589</v>
+        <v>0.0966353497022475</v>
       </c>
       <c r="U3" t="n">
-        <v>0.00880998949664902</v>
+        <v>0.0175382891813646</v>
       </c>
       <c r="V3" t="n">
-        <v>0.153951524413952</v>
+        <v>-0.0217683700198446</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.000663927416267805</v>
+        <v>-0.025007528571517</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0314487987340588</v>
+        <v>-0.00594697343484887</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0104940198825143</v>
+        <v>0.00718843060368204</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.120614096583618</v>
+        <v>0.0791304082566166</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0395366234798004</v>
+        <v>-0.0221341414530939</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.00483664802590881</v>
+        <v>-0.0271665153679097</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0448484393642228</v>
+        <v>-0.770302815554919</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.979856773532109</v>
+        <v>0.00687099960299616</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.00946405202923316</v>
+        <v>0.034725840262175</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0299792687730638</v>
+        <v>3.17771325978908</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0676550308085177</v>
+        <v>9.45590659332335</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.428334473648326</v>
+        <v>15.5290344904718</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0176716952140151</v>
+        <v>0.0786333169234391</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.99457282713957</v>
+        <v>0.44603511539236</v>
       </c>
       <c r="AK3" t="n">
-        <v>9.33087764879962</v>
+        <v>0.420761142313532</v>
       </c>
       <c r="AL3" t="n">
-        <v>18.4522285717446</v>
+        <v>0.117825175411432</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0061453313948757</v>
+        <v>-0.603686124644861</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.00225860547147051</v>
+        <v>0.323806812980551</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.750346854615959</v>
+        <v>-0.671327616035061</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.61132819678966</v>
+        <v>-0.0221341414530939</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.570642261293896</v>
+        <v>-1.78849019467855</v>
       </c>
       <c r="AR3" t="n">
-        <v>-1.64233403755784</v>
+        <v>0.594774917323201</v>
       </c>
       <c r="AS3" t="n">
-        <v>-1.02583927315905</v>
+        <v>-1.71738724827605</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.00294416403904381</v>
+        <v>-0.472378788154204</v>
       </c>
       <c r="AU3" t="n">
-        <v>-54.7328531296817</v>
+        <v>0.0154628528350774</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.000288483276125728</v>
+        <v>-5.42457052529447</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.082824488992623</v>
+        <v>-0.010042058696367</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4624905822093</v>
+        <v>-0.0221341414530939</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.43634612626294</v>
+        <v>-0.0689272219917101</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.135549745516491</v>
+        <v>-0.00596079190927153</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.591491777146069</v>
+        <v>-0.124494038406793</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.335845820187956</v>
+        <v>0.0396977072599543</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.638033078567718</v>
+        <v>-0.00299484608859408</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-0.0900985847101783</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.430405702605618</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.00420126331280438</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-0.00686645883417283</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-0.00212758389752027</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-0.733223676197547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0231223452917566</v>
+        <v>-0.0203743776103109</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00607943862543952</v>
+        <v>0.00779730675007682</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.14773979853497</v>
+        <v>-0.0839658046014768</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00327351229439764</v>
+        <v>-0.160573643927154</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.158389557612493</v>
+        <v>0.0116350506174326</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00046102281234004</v>
+        <v>0.201525623572652</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0822441648432457</v>
+        <v>-0.0181058995709713</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0275514900002306</v>
+        <v>-0.278648268623139</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.354402822943949</v>
+        <v>-0.37338220636912</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.60516487793658</v>
+        <v>-0.204154783015747</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.240361938570053</v>
+        <v>-0.0837003183939476</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.141673309474381</v>
+        <v>-0.0988475340227592</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.111873501177523</v>
+        <v>-0.141210710616172</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.00240211501520752</v>
+        <v>-0.0466720427614512</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.19943066178769</v>
+        <v>-0.0223308923262131</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0834314990291737</v>
+        <v>0.0503303137154591</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0190860365831881</v>
+        <v>-0.0794524172790022</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0302010313950094</v>
+        <v>-0.00749851703955117</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.113482328599826</v>
+        <v>-0.193174881389105</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0138084467571134</v>
+        <v>-0.0732747438842462</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.228174030680139</v>
+        <v>-0.00278835022062918</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.108265910886466</v>
+        <v>-0.0166067860871565</v>
       </c>
       <c r="X4" t="n">
-        <v>0.37809336665473</v>
+        <v>-0.00184761400226204</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0363040488376597</v>
+        <v>-0.0100046443402444</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.0444248226279106</v>
+        <v>-0.0963687065038142</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0187589672479461</v>
+        <v>-0.0203743776103109</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.0104296009094113</v>
+        <v>0.238507466780687</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.233695865262473</v>
+        <v>-0.0055179876751338</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0223984978056895</v>
+        <v>0.265749097758507</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.228960554015375</v>
+        <v>-0.0322109025191484</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.00683283553171669</v>
+        <v>-3.63618198377684</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.396109190787682</v>
+        <v>3.19198075695889</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.340104887889717</v>
+        <v>12.7284237561243</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.00242350092105816</v>
+        <v>0.282585669768487</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.27464477306545</v>
+        <v>1.08459192358979</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.02908912860439</v>
+        <v>1.08405563486571</v>
       </c>
       <c r="AL4" t="n">
-        <v>9.10941214768587</v>
+        <v>1.69130769280195</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.00455916304669268</v>
+        <v>2.74556373901538</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.00233084139640067</v>
+        <v>0.75630921144054</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.00665567797918917</v>
+        <v>2.08339580005781</v>
       </c>
       <c r="AP4" t="n">
-        <v>-3.47072953260904</v>
+        <v>-0.0203743776103109</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.49816815723862</v>
+        <v>-4.31875399729239</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.16544223161076</v>
+        <v>3.56540005694909</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0.809330150192137</v>
+        <v>-0.782589675263861</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0123788182431956</v>
+        <v>-1.41801144666476</v>
       </c>
       <c r="AU4" t="n">
-        <v>-55.2718444874878</v>
+        <v>-0.012636845194835</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.00285798604666008</v>
+        <v>-42.063917768553</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.260407074358959</v>
+        <v>-0.0170909351015783</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.05879960134535</v>
+        <v>-0.0203743776103109</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.06584031438222</v>
+        <v>0.391618492627779</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.66726029383728</v>
+        <v>0.0545735720995601</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.7098576358129</v>
+        <v>-0.0654341902052057</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.684307981383821</v>
+        <v>0.0180099487089462</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.04698566450362</v>
+        <v>-0.017640294352863</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.271938752196663</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.0988875903309765</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.000651213151715339</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-0.00273756632938549</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.00197807540185887</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0.00507901594179504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0324663225072889</v>
+        <v>-0.0325286853506883</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.166215700740868</v>
+        <v>-0.122014764713604</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.120669137561437</v>
+        <v>-0.0980898804713043</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0109782397113156</v>
+        <v>-0.0460995270754599</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.052285266456603</v>
+        <v>-0.0856219006310501</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.122115766069116</v>
+        <v>-0.169157530573119</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.279136292518863</v>
+        <v>-0.0943666974336294</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.137989257918811</v>
+        <v>-0.046366232871423</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0803738045413948</v>
+        <v>-0.130678648965293</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.214734701668143</v>
+        <v>-0.048917726788189</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.116455558293303</v>
+        <v>-0.0457414901501482</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0153112940549747</v>
+        <v>-0.026573481692435</v>
       </c>
       <c r="N5" t="n">
-        <v>0.00219969242431</v>
+        <v>-0.0692464942458135</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.00365390615278674</v>
+        <v>-0.0647205616522289</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.072604860659489</v>
+        <v>-0.0278724541611876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.0746048670785395</v>
+        <v>-0.0218776303200323</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0484833416077472</v>
+        <v>-0.0651659970916472</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0328770558765441</v>
+        <v>-0.094704517426158</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0726030471907681</v>
+        <v>-0.0493827395147707</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.136038244246167</v>
+        <v>-0.0662767394077226</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.119161457905417</v>
+        <v>-0.0175848898050814</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0763233397645512</v>
+        <v>-0.0471718472427118</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0562766277540667</v>
+        <v>0.0108436371775343</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000734790999835218</v>
+        <v>0.0064511956297064</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.133402318512002</v>
+        <v>-0.000922632744525248</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0248703690066781</v>
+        <v>-0.0325286853506883</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.010809143305739</v>
+        <v>-0.240200751296639</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.281025846643375</v>
+        <v>-0.602380310114915</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.884210092861481</v>
+        <v>-0.239853211250507</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.269938910896267</v>
+        <v>0.034137452496366</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0459854587189053</v>
+        <v>12.8592769993275</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.585794973347371</v>
+        <v>-0.192251643736603</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.947078300447766</v>
+        <v>26.77912495624</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.05405593251204</v>
+        <v>-0.197700988707845</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.7781446746757</v>
+        <v>-0.480525696225354</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.123486418701235</v>
+        <v>-0.491243416945087</v>
       </c>
       <c r="AL5" t="n">
-        <v>23.8406867999363</v>
+        <v>-0.517661915067306</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.00100558661187555</v>
+        <v>-0.268031660005875</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.000380112189937309</v>
+        <v>-0.416594915570839</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.635178921432065</v>
+        <v>-0.311494422645666</v>
       </c>
       <c r="AP5" t="n">
-        <v>-2.91897478707734</v>
+        <v>-0.0325286853506883</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.91003164296706</v>
+        <v>-3.27804295023073</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1.70816139431166</v>
+        <v>0.103643179064499</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.283897965015803</v>
+        <v>-1.31587084830012</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.00801044457928202</v>
+        <v>-0.38010878600959</v>
       </c>
       <c r="AU5" t="n">
-        <v>-47.1614467565665</v>
+        <v>-0.00859639314104966</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.00670244124314961</v>
+        <v>-6.61747476724499</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.186541029305164</v>
+        <v>-0.00238507996928706</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.478144308895526</v>
+        <v>-0.0325286853506883</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.489153250890213</v>
+        <v>-0.0623337941018985</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.494099734486002</v>
+        <v>-0.0139735040891263</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.255775563613427</v>
+        <v>-0.0889789398903094</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.4054637465681</v>
+        <v>0.0267904630273537</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.220934910412396</v>
+        <v>0.000275088542728966</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.498774154428945</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.805735820374807</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.00761274426643998</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.0000407778520189205</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.000485969982432017</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0.622655757258443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0174185181285461</v>
+        <v>0.0111896546494327</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0468214705337483</v>
+        <v>0.110123897161324</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0792633593641781</v>
+        <v>0.0594823394641421</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0176707917790005</v>
+        <v>0.00138620103745199</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0784262255843109</v>
+        <v>-0.0410338671533221</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0227539512761</v>
+        <v>-0.0524689124097606</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0128221912376309</v>
+        <v>-0.00777819389424965</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0176457430026022</v>
+        <v>0.183072132285433</v>
       </c>
       <c r="J6" t="n">
-        <v>0.146035098543115</v>
+        <v>-0.0140515295826258</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.216846424139433</v>
+        <v>0.085549861147115</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0590795736732982</v>
+        <v>0.0722057873717832</v>
       </c>
       <c r="M6" t="n">
-        <v>0.101144051080809</v>
+        <v>0.0581279308629707</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0474414469837844</v>
+        <v>0.0594315464166114</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0000805503871144751</v>
+        <v>-0.0139516952096968</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0339873498176309</v>
+        <v>0.0972308094678789</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.000890911928162337</v>
+        <v>-0.0395915370136168</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0275285722095848</v>
+        <v>0.0291116808889536</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0290681039008357</v>
+        <v>-0.0130612761644817</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0158079669891685</v>
+        <v>0.070693667754269</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0290082092164288</v>
+        <v>0.0248295369766438</v>
       </c>
       <c r="V6" t="n">
-        <v>0.050493402177723</v>
+        <v>-0.0202219764604383</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0122476206846354</v>
+        <v>-0.015961298438483</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0044581230250738</v>
+        <v>0.0145774880585199</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0200920123602989</v>
+        <v>-0.000123590283420022</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0916377737790623</v>
+        <v>0.0597279019483435</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.017870439627708</v>
+        <v>0.0111896546494327</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.00179248807091937</v>
+        <v>-0.0748923204047765</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.179116126690656</v>
+        <v>-0.423678741868557</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.816986093301368</v>
+        <v>-0.0594431157486579</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.165130507762633</v>
+        <v>-0.00900767875704805</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.00787757354384562</v>
+        <v>-2.61132807038946</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.149183124542779</v>
+        <v>-6.89076795398724</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.214564195736955</v>
+        <v>-29.9470519040486</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0103257713616061</v>
+        <v>-0.0332608460612143</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-2.17015305213633</v>
+        <v>0.137839947010808</v>
       </c>
       <c r="AK6" t="n">
-        <v>-6.73291222609451</v>
+        <v>0.13637941094463</v>
       </c>
       <c r="AL6" t="n">
-        <v>-26.2612658336117</v>
+        <v>-0.122399969203203</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.00421484800858861</v>
+        <v>-0.388364951192247</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.000756207406482632</v>
+        <v>-0.0224633016088872</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.25671499266949</v>
+        <v>-0.595670602562299</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.213709001945531</v>
+        <v>0.0111896546494327</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-2.30110305982401</v>
+        <v>0.647163158559724</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.768699819037765</v>
+        <v>-3.1904011933925</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.423605900767362</v>
+        <v>-0.453595963951475</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0262453094585041</v>
+        <v>0.622946781722748</v>
       </c>
       <c r="AU6" t="n">
-        <v>-78.4187515769036</v>
+        <v>-0.00569921810945458</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.0191919822999032</v>
+        <v>-15.8994468340273</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0314582741135415</v>
+        <v>0.00309005947437109</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.139297828468957</v>
+        <v>0.0111896546494327</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.139131862751789</v>
+        <v>-0.0650535239568293</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.108132316583906</v>
+        <v>-0.014554793648164</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.373787790687732</v>
+        <v>-0.0879917342022967</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0267511092881613</v>
+        <v>0.0198687079575747</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.486729340780307</v>
+        <v>0.00822729452788746</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.0877323322809686</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.190653634970529</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.01883440585126</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.00503272571077103</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.000799265942887367</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.242091355144987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.00691612544437957</v>
+        <v>0.0016916141435206</v>
       </c>
       <c r="C7" t="n">
-        <v>0.129067578865055</v>
+        <v>0.0554788106625309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.169415730548461</v>
+        <v>0.0614207298724778</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000264353547362193</v>
+        <v>-0.0145088813068838</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0367559240497505</v>
+        <v>0.110606121684165</v>
       </c>
       <c r="G7" t="n">
-        <v>0.155655754392645</v>
+        <v>0.0680502058653062</v>
       </c>
       <c r="H7" t="n">
-        <v>0.146517810957742</v>
+        <v>0.0918115939259928</v>
       </c>
       <c r="I7" t="n">
-        <v>0.165216074927616</v>
+        <v>0.0601744798308835</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0703604823100495</v>
+        <v>-0.188331569638821</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0818838433398142</v>
+        <v>0.0406597387657337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.062538753708422</v>
+        <v>0.103548025235894</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0933773973046913</v>
+        <v>0.00202098858221799</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0040318022594902</v>
+        <v>0.0874935060532407</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00244358896926721</v>
+        <v>0.110979265869809</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0913765089216508</v>
+        <v>0.0239107660601627</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.134761493342818</v>
+        <v>0.00273469106055817</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0452616001040136</v>
+        <v>0.105554071475889</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0323551807642106</v>
+        <v>0.0951759245750315</v>
       </c>
       <c r="T7" t="n">
-        <v>0.12517766410601</v>
+        <v>0.0383246834572868</v>
       </c>
       <c r="U7" t="n">
-        <v>0.160716786100458</v>
+        <v>0.111511245163811</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0611183592845519</v>
+        <v>-0.000156771078757567</v>
       </c>
       <c r="W7" t="n">
-        <v>0.130890655867303</v>
+        <v>-0.000460941522093797</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.159992077167176</v>
+        <v>-0.000652098137484839</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0411814407999125</v>
+        <v>-0.0064557992462484</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.131634257190796</v>
+        <v>0.117467098864332</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0106850039893398</v>
+        <v>0.0016916141435206</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.020816855623476</v>
+        <v>-0.283628703906132</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.379221354916522</v>
+        <v>0.138826687668009</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.141344443006081</v>
+        <v>-0.309927730022684</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.399734046193737</v>
+        <v>-0.00113082445223893</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.00102837543173717</v>
+        <v>-4.93482380993126</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.376978367519878</v>
+        <v>-7.22063560926808</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.628115145351389</v>
+        <v>19.8455533951558</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.00394032050307432</v>
+        <v>-0.0180925555466997</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-4.6687125332299</v>
+        <v>0.418246721515095</v>
       </c>
       <c r="AK7" t="n">
-        <v>-6.92443539248427</v>
+        <v>0.424361583032095</v>
       </c>
       <c r="AL7" t="n">
-        <v>19.5970448807871</v>
+        <v>0.289059744010996</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0153857621732862</v>
+        <v>0.308994584925497</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.00268103389106456</v>
+        <v>0.159101834134017</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.405495893536491</v>
+        <v>0.197995368697023</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.54087595454043</v>
+        <v>0.0016916141435206</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-5.88178278941442</v>
+        <v>1.12134033295021</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.52436944270199</v>
+        <v>-5.94298722785559</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.832665800202356</v>
+        <v>2.15545868450043</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0200120697319191</v>
+        <v>1.54602068082667</v>
       </c>
       <c r="AU7" t="n">
-        <v>-82.6804046970864</v>
+        <v>-0.00839102625197632</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0107251563601676</v>
+        <v>-32.1995523411849</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0134930153805249</v>
+        <v>0.0131038302273313</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.43035979873478</v>
+        <v>0.0016916141435206</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.437201177324331</v>
+        <v>-0.170172304400208</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.311948333365419</v>
+        <v>-0.0484867898515297</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.292622043141118</v>
+        <v>-0.130900303696153</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.162785037209128</v>
+        <v>-0.0097474141827183</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.285883059554294</v>
+        <v>0.0262124964709996</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.357638558366775</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.563513299647262</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.018776500720234</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.0165749855340629</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.00341200918641746</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.420820327277151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0240185488176036</v>
+        <v>0.0237992005741522</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.142878131736415</v>
+        <v>-0.134831925330972</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.068480633047916</v>
+        <v>-0.106665696028367</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.000344619277509116</v>
+        <v>-0.00210520011203225</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0789698229599437</v>
+        <v>-0.0041952574902393</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0486915226342171</v>
+        <v>-0.0259083380395657</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0583501562862704</v>
+        <v>-0.0493917054781802</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0911787491887938</v>
+        <v>-0.0883645155060498</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0363250513479566</v>
+        <v>0.309219299525867</v>
       </c>
       <c r="K8" t="n">
-        <v>0.314941604298878</v>
+        <v>0.0567337331081234</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0700300804620231</v>
+        <v>-0.0715951342108236</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.00027545192557854</v>
+        <v>-0.0463280683589995</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0510175587440893</v>
+        <v>0.0138111941148235</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00214579905667849</v>
+        <v>0.0861825699207249</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0338619364880914</v>
+        <v>0.263100653547779</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0955046499193713</v>
+        <v>0.0241502037875185</v>
       </c>
       <c r="R8" t="n">
-        <v>0.310844157602739</v>
+        <v>0.0823716821161474</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0457254703230984</v>
+        <v>-0.0423401208623003</v>
       </c>
       <c r="T8" t="n">
-        <v>0.09931195990929</v>
+        <v>0.0757260764774565</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0911112525696696</v>
+        <v>0.0918117366690664</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0731268687803353</v>
+        <v>0.0317868662453055</v>
       </c>
       <c r="W8" t="n">
-        <v>0.107486212294883</v>
+        <v>0.0433669709025216</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.486127420698196</v>
+        <v>-0.00203471874096844</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.0083723322236002</v>
+        <v>-0.00704514598014381</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.581241430149459</v>
+        <v>-0.0612103131719041</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.10179554820701</v>
+        <v>0.0237992005741522</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00709228305161633</v>
+        <v>-0.0196716387334885</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.0500577508769217</v>
+        <v>1.71905337412741</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.2141066039324</v>
+        <v>-0.0529446881570243</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.0718784534814457</v>
+        <v>0.0328225723340265</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0249295928990684</v>
+        <v>-9.01272307721351</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.510361599788161</v>
+        <v>-16.3377612856515</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.67708316183928</v>
+        <v>-92.0387708878531</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.0194853234805728</v>
+        <v>-0.324050522133134</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-21.1264698751079</v>
+        <v>-1.96214937859133</v>
       </c>
       <c r="AK8" t="n">
-        <v>-15.954337821265</v>
+        <v>-1.89546618886632</v>
       </c>
       <c r="AL8" t="n">
-        <v>-92.1694443285815</v>
+        <v>-1.89651190208578</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0168320296249333</v>
+        <v>-1.22021097105653</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.00727996290028117</v>
+        <v>-1.22631695627796</v>
       </c>
       <c r="AO8" t="n">
-        <v>2.10174089857123</v>
+        <v>-0.810419476847576</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.58718448809795</v>
+        <v>0.0237992005741522</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-6.52210905953343</v>
+        <v>11.0611048510848</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.40540326919446</v>
+        <v>-8.13657157043532</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.32775366674893</v>
+        <v>1.89965622981696</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0.0171572753679531</v>
+        <v>1.2231669853248</v>
       </c>
       <c r="AU8" t="n">
-        <v>-61.4288260994301</v>
+        <v>-0.00797225887403143</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.0358690398195845</v>
+        <v>-14.3772288344109</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.305065515999568</v>
+        <v>0.0976463849176611</v>
       </c>
       <c r="AX8" t="n">
-        <v>-1.96358071938279</v>
+        <v>0.0237992005741522</v>
       </c>
       <c r="AY8" t="n">
-        <v>-1.89509858275947</v>
+        <v>-0.160721921099835</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-1.86610105782767</v>
+        <v>0.00718328310658834</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.19802927011539</v>
+        <v>0.623368914024887</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.1887209071013</v>
+        <v>-0.104572526869896</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0.713444660329237</v>
+        <v>-0.00235061950876203</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.364227869492569</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.868083983240932</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.0457772676852642</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.0175497742443751</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.00697314120095147</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.10000862327134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0174908320019528</v>
+        <v>-0.0107601668485331</v>
       </c>
       <c r="C9" t="n">
-        <v>0.13568260175206</v>
+        <v>0.0694253778846952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0754143109142353</v>
+        <v>0.0346589884140389</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.010691081458131</v>
+        <v>0.111605333198221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.098056076468343</v>
+        <v>0.0962525363404283</v>
       </c>
       <c r="G9" t="n">
-        <v>0.131175547616267</v>
+        <v>-0.00746862204342071</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.00238439230045549</v>
+        <v>0.0855536155303945</v>
       </c>
       <c r="I9" t="n">
-        <v>0.107366926460519</v>
+        <v>0.0504734259398501</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.00627481187776251</v>
+        <v>-0.208271122741779</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00965164166310985</v>
+        <v>0.0986245611203094</v>
       </c>
       <c r="L9" t="n">
-        <v>0.223536312888674</v>
+        <v>0.067673495916023</v>
       </c>
       <c r="M9" t="n">
-        <v>0.100062464882949</v>
+        <v>-0.0108437631294407</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.00123821521309272</v>
+        <v>0.0786633420934962</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.000547469062032902</v>
+        <v>0.0415623718171625</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0609727441017776</v>
+        <v>-0.0324191136737228</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0586888694274335</v>
+        <v>-0.0027053805893549</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.0202764467280958</v>
+        <v>0.0383287535447493</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0353065435195774</v>
+        <v>0.09066077539429</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0517938936893557</v>
+        <v>0.104722423510447</v>
       </c>
       <c r="U9" t="n">
-        <v>0.108598690330434</v>
+        <v>0.0416848994848347</v>
       </c>
       <c r="V9" t="n">
-        <v>0.24682934346228</v>
+        <v>-0.00113998729489261</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0542251384176365</v>
+        <v>0.016912909640061</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0561483057766908</v>
+        <v>-0.000969293831558328</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.0130528623435683</v>
+        <v>-0.00545927080555194</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.085928278767992</v>
+        <v>-0.0674828256708319</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0327588260058886</v>
+        <v>-0.0107601668485331</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00389243029165365</v>
+        <v>0.120325299563882</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.176084822516791</v>
+        <v>-0.314908419026853</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.453610576160843</v>
+        <v>0.0986064075879345</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.143914658198225</v>
+        <v>-0.0568021735079</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0469722932445974</v>
+        <v>-0.624784079803963</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.052173765755688</v>
+        <v>24.7971160064304</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.599044462551007</v>
+        <v>21.1224527119021</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.000496698986104357</v>
+        <v>0.229753807778225</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.616122964396628</v>
+        <v>1.05828541957378</v>
       </c>
       <c r="AK9" t="n">
-        <v>25.2188168051877</v>
+        <v>1.06438261422827</v>
       </c>
       <c r="AL9" t="n">
-        <v>23.1352462949379</v>
+        <v>0.785942009562261</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0014306330060762</v>
+        <v>0.487882730365099</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.000306689842651634</v>
+        <v>0.697195612240213</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.114290623056911</v>
+        <v>-0.0374455911788562</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.504282948539545</v>
+        <v>-0.0107601668485331</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.799412549540052</v>
+        <v>-1.67028852900829</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.672004072160517</v>
+        <v>-0.0109312412913779</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0190651768752069</v>
+        <v>-0.191921675231057</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0.0176777000848441</v>
+        <v>-0.336248048840461</v>
       </c>
       <c r="AU9" t="n">
-        <v>-75.8524352180739</v>
+        <v>-0.0114423256380421</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00701312160205603</v>
+        <v>-38.3424138223202</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.22126532943707</v>
+        <v>-0.0208097444155831</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.06090519050061</v>
+        <v>-0.0107601668485331</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.06820394542718</v>
+        <v>0.074872943332801</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.786674184179406</v>
+        <v>-0.0309050695110712</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.453264170147379</v>
+        <v>-0.085804112752481</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.684598442080132</v>
+        <v>0.0321586612015137</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.0308550581575748</v>
+        <v>0.00173258813346108</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.0206447053958451</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0.56047013214129</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.000343998372898837</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.00197200880993254</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.000229650166180577</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0.10211662579286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00146946948053254</v>
+        <v>0.00379607876635765</v>
       </c>
       <c r="C10" t="n">
-        <v>0.14583823766205</v>
+        <v>0.194361998892864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.054803178034063</v>
+        <v>0.0975994435577037</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.00487533020688282</v>
+        <v>0.0233719976102421</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0512070848137356</v>
+        <v>0.0395856823912233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00733984103776776</v>
+        <v>0.0698733751954535</v>
       </c>
       <c r="H10" t="n">
-        <v>0.106518679865866</v>
+        <v>0.0705558338791445</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0548040878808512</v>
+        <v>0.0849547857042242</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0496466530202185</v>
+        <v>0.0601430323680632</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0829952133151776</v>
+        <v>0.0292138845299469</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.055166214187364</v>
+        <v>0.108725795381303</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0893260923882625</v>
+        <v>0.0660182326205712</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0410964549823381</v>
+        <v>0.00620438066090511</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0000997790771453795</v>
+        <v>0.0307882196430586</v>
       </c>
       <c r="P10" t="n">
-        <v>0.022280239518344</v>
+        <v>-0.0506951096157239</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0296557659602465</v>
+        <v>0.013325731189545</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.0478076541324041</v>
+        <v>0.0325507305764863</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0446671123613049</v>
+        <v>0.0637311713530358</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0297192660126549</v>
+        <v>0.0218218940632773</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0535521897797193</v>
+        <v>0.0274333514639498</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0665090375741618</v>
+        <v>-0.00351881208243151</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0275581463308602</v>
+        <v>-0.00206017283480927</v>
       </c>
       <c r="X10" t="n">
-        <v>0.200749288220886</v>
+        <v>-0.00540575234929896</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0187777877171677</v>
+        <v>-0.00579879783185996</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0769594642190067</v>
+        <v>0.000139235351569367</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00509270268610654</v>
+        <v>0.00379607876635765</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.000628782152515455</v>
+        <v>-0.0342589796517672</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.0155375590398872</v>
+        <v>-0.317730159419209</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.390950982823893</v>
+        <v>-0.0346914560561887</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.0139201629956971</v>
+        <v>0.00300079312805353</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0055832790336976</v>
+        <v>9.18564175834393</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.201853508728521</v>
+        <v>2.60351806295416</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.375325543129236</v>
+        <v>38.9228280039465</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.00540986861055448</v>
+        <v>-0.0079908077062404</v>
       </c>
       <c r="AJ10" t="n">
-        <v>11.351434812032</v>
+        <v>0.0993371854900619</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.21634942021883</v>
+        <v>0.0648298521035288</v>
       </c>
       <c r="AL10" t="n">
-        <v>38.7936039090815</v>
+        <v>0.120572232824682</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.0158029366215888</v>
+        <v>-0.117960350491315</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.00386628853452755</v>
+        <v>0.0824821535077846</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.53566095827463</v>
+        <v>0.322043412432475</v>
       </c>
       <c r="AP10" t="n">
-        <v>-3.31169825610503</v>
+        <v>0.00379607876635765</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.50851207763957</v>
+        <v>-3.36054905774655</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.371808545791506</v>
+        <v>0.125640023711585</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.635961343774357</v>
+        <v>-1.05862112080309</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.000802453538135034</v>
+        <v>-0.969569942067806</v>
       </c>
       <c r="AU10" t="n">
-        <v>88.0294538851699</v>
+        <v>-0.00465036666388241</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.00176327341285087</v>
+        <v>20.4716391934634</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.0137383264052036</v>
+        <v>-0.00852965206021429</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.067884416083123</v>
+        <v>0.00379607876635765</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.030707452325329</v>
+        <v>0.123513363905274</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0470703164423293</v>
+        <v>0.0165868695718829</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.0813725133579004</v>
+        <v>-0.0682606175468987</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0658196203153378</v>
+        <v>0.00640762906621618</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.060545262964154</v>
+        <v>-0.00231622520835979</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.226721715917034</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.255688366175892</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.00678206785536286</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.01638452748375</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.00423125097371813</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0.544121789461287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0178464988232881</v>
+        <v>0.00330590970407478</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0629793024268025</v>
+        <v>0.147380940790155</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0615048313347812</v>
+        <v>0.0860160295965499</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0069770010828704</v>
+        <v>0.02995211991031</v>
       </c>
       <c r="F11" t="n">
-        <v>0.108419507507116</v>
+        <v>0.00953556340121431</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.010325410056975</v>
+        <v>0.0558181981008451</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0262096097421635</v>
+        <v>0.0296954906944263</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00962109134350622</v>
+        <v>0.0158617624856274</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0457779870722685</v>
+        <v>0.313060253546427</v>
       </c>
       <c r="K11" t="n">
-        <v>0.47162361146996</v>
+        <v>-0.0427652547046527</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0139356839565808</v>
+        <v>0.0468517688481327</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0239862487954879</v>
+        <v>0.109958567821692</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0974759726825871</v>
+        <v>0.042769586516405</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.000147768769106434</v>
+        <v>0.0211958266043548</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0716575617910246</v>
+        <v>-0.0434899261813493</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0137032013814164</v>
+        <v>-0.000646349904212877</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.0477705956569412</v>
+        <v>0.03321280075391</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0400537290091095</v>
+        <v>0.0240534255699838</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0253253425282462</v>
+        <v>-0.0505408090917457</v>
       </c>
       <c r="U11" t="n">
-        <v>0.00354961728387915</v>
+        <v>0.0233233898465209</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.00988390461702513</v>
+        <v>-0.0160402896903781</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0173914599993696</v>
+        <v>0.0257710771195284</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.073402980865313</v>
+        <v>0.0169332582755317</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0.00435411119098123</v>
+        <v>0.0533113040488226</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.105707567257831</v>
+        <v>0.1346138312419</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.0253512584624609</v>
+        <v>0.00330590970407478</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.00943238858817275</v>
+        <v>-0.0354567410752362</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.025639284531466</v>
+        <v>0.128949509529747</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.475179994960019</v>
+        <v>-0.0422757744771231</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0245298501227274</v>
+        <v>-0.0174550436587456</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.0230719882505173</v>
+        <v>6.42513956495643</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.0218479633895193</v>
+        <v>-3.78655200623572</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.443035367206869</v>
+        <v>28.9449742236903</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0338493507984856</v>
+        <v>-0.0951203534760066</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8.01502598273254</v>
+        <v>-0.280465339930393</v>
       </c>
       <c r="AK11" t="n">
-        <v>-4.07956121527866</v>
+        <v>-0.315517269456471</v>
       </c>
       <c r="AL11" t="n">
-        <v>26.2396165289487</v>
+        <v>-0.268724626977033</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.00884812996954087</v>
+        <v>-0.489446482450284</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.00203374380844135</v>
+        <v>-0.198475120765655</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.397063484616447</v>
+        <v>-0.48313178901756</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1.56549255543596</v>
+        <v>0.00330590970407478</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.58336673699867</v>
+        <v>-1.42640909208072</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.398544986204642</v>
+        <v>5.91211095973774</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.0523423042670103</v>
+        <v>-0.895613718645758</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0066170685694023</v>
+        <v>-0.823422918814776</v>
       </c>
       <c r="AU11" t="n">
-        <v>193.498749875174</v>
+        <v>0.0198046521585685</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0238707066794256</v>
+        <v>64.7608500031866</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.0950316214115113</v>
+        <v>0.00442311960733503</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.298033122240578</v>
+        <v>0.00330590970407478</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.338808805040747</v>
+        <v>0.0725586485713087</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.298926174447338</v>
+        <v>0.00457331816569248</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0.504709147676449</v>
+        <v>-0.0794686588701281</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0.188775434293661</v>
+        <v>-0.022730959003571</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.585389908696705</v>
+        <v>0.00562799823828984</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.132832947960337</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.482211586012499</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.0253117043650773</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0.0103886763340441</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-0.00230109366776357</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0.416902965091475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0573127393545969</v>
+        <v>0.0574869546975551</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0663872033721817</v>
+        <v>0.0627569214130735</v>
       </c>
       <c r="D12" t="n">
-        <v>0.200556941555263</v>
+        <v>0.16928729582152</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0398771091263255</v>
+        <v>0.181161651205074</v>
       </c>
       <c r="F12" t="n">
-        <v>0.418560266759261</v>
+        <v>0.0151993913420284</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0531158071335693</v>
+        <v>0.0337106585056498</v>
       </c>
       <c r="H12" t="n">
-        <v>0.024382376949425</v>
+        <v>0.0663592388653425</v>
       </c>
       <c r="I12" t="n">
-        <v>0.11870431420876</v>
+        <v>0.12082021118173</v>
       </c>
       <c r="J12" t="n">
-        <v>0.165345018773324</v>
+        <v>0.467253145695357</v>
       </c>
       <c r="K12" t="n">
-        <v>0.424152086271421</v>
+        <v>0.0122705756134747</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0539955567792511</v>
+        <v>0.0523986716894069</v>
       </c>
       <c r="M12" t="n">
-        <v>0.107611480129375</v>
+        <v>0.131205113193585</v>
       </c>
       <c r="N12" t="n">
-        <v>0.144498457613103</v>
+        <v>0.198025239949699</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00393601006762635</v>
+        <v>0.0571106148616265</v>
       </c>
       <c r="P12" t="n">
-        <v>0.394726240048427</v>
+        <v>-0.00197631555638445</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.109769188723225</v>
+        <v>0.0331111192044257</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0145946783301722</v>
+        <v>0.094141686407852</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0508831574852769</v>
+        <v>0.0506071158844021</v>
       </c>
       <c r="T12" t="n">
-        <v>0.176611580460272</v>
+        <v>-0.00172738073185696</v>
       </c>
       <c r="U12" t="n">
-        <v>0.106200430503057</v>
+        <v>0.0855989607660336</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0773866344749552</v>
+        <v>0.0325476245037432</v>
       </c>
       <c r="W12" t="n">
-        <v>0.172371861431248</v>
+        <v>0.0342387392245079</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.22668078070692</v>
+        <v>-0.0158690518044377</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.0156281385556694</v>
+        <v>-0.00954756689330399</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.157306119341423</v>
+        <v>-0.0634160524993205</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.0563517383892185</v>
+        <v>0.0574869546975551</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.0039508721034878</v>
+        <v>0.10215117539764</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.221177070721894</v>
+        <v>1.02430888453424</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.49398042395309</v>
+        <v>0.0779898973230106</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.204272201904011</v>
+        <v>0.0256468391870354</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.00327486459837969</v>
+        <v>10.3825789897294</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.312549891948876</v>
+        <v>-11.8074921105374</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.29176669356309</v>
+        <v>-12.7054687916566</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0369469250798705</v>
+        <v>-0.280826175534107</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.94566145575328</v>
+        <v>-1.96187907500934</v>
       </c>
       <c r="AK12" t="n">
-        <v>-11.576259655946</v>
+        <v>-1.89482506440636</v>
       </c>
       <c r="AL12" t="n">
-        <v>-13.3544011627236</v>
+        <v>-1.59565512176468</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.00793557625253951</v>
+        <v>-1.18205595693551</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.000397966761397438</v>
+        <v>-1.22766947552045</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.273834933257514</v>
+        <v>-1.35410658786014</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.11905632800766</v>
+        <v>0.0574869546975551</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.58249225031273</v>
+        <v>4.24082559502784</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.51884336244237</v>
+        <v>6.72187461778694</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.823011970066302</v>
+        <v>3.20570944017448</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0125022848798439</v>
+        <v>1.13064796511604</v>
       </c>
       <c r="AU12" t="n">
-        <v>152.552559046767</v>
+        <v>0.0235818025916482</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0187593733811222</v>
+        <v>69.5078139826724</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.259399471274994</v>
+        <v>-0.0422658990073197</v>
       </c>
       <c r="AX12" t="n">
-        <v>-1.89681375236947</v>
+        <v>0.0574869546975551</v>
       </c>
       <c r="AY12" t="n">
-        <v>-1.82871883078827</v>
+        <v>-0.25086384606443</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-1.5379708614156</v>
+        <v>-0.0156387845446128</v>
       </c>
       <c r="BA12" t="n">
-        <v>-1.14601332548887</v>
+        <v>0.0495522387392417</v>
       </c>
       <c r="BB12" t="n">
-        <v>-1.17657252531818</v>
+        <v>-0.0605144058354366</v>
       </c>
       <c r="BC12" t="n">
-        <v>-1.31643778478499</v>
+        <v>0.0059130078110877</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.283442369376223</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.25678752951199</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.0336430218234816</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.00942422520285237</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.00110592499070373</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.265324252837569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0269275376082717</v>
+        <v>-0.0232016417953345</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.232858854343251</v>
+        <v>-0.330280240826589</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.237879961250249</v>
+        <v>-0.163792050368117</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0218917057686247</v>
+        <v>-0.167271902499466</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.22887593375028</v>
+        <v>-0.0851775313067445</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.109127499135334</v>
+        <v>-0.111206748686996</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0632246237733879</v>
+        <v>-0.133451925871853</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.161646209284398</v>
+        <v>-0.237554391414924</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.21748526500659</v>
+        <v>-0.170995817172662</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0000272874702155253</v>
+        <v>-0.162021848639044</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.148857670317263</v>
+        <v>-0.181026454047777</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.208516918319357</v>
+        <v>-0.123243924866692</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.106836295492663</v>
+        <v>-0.186937087540904</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.00520570775677093</v>
+        <v>-0.116101471196711</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.267482501264516</v>
+        <v>-0.146379752900888</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.16278269177965</v>
+        <v>-0.0352814659320229</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.144727085345821</v>
+        <v>-0.172749983022184</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0314141083608391</v>
+        <v>-0.127267221710903</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.209229758342455</v>
+        <v>-0.150969210942737</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.148558120094508</v>
+        <v>-0.16932861076034</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.140859408925929</v>
+        <v>0.0259254616774935</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.208642230516217</v>
+        <v>-0.00713453249345702</v>
       </c>
       <c r="X13" t="n">
-        <v>0.272621492324752</v>
+        <v>-0.00388917318968417</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0274690632383197</v>
+        <v>-0.010783841722055</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.000577229813510477</v>
+        <v>-0.0684190765815336</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0417587352074231</v>
+        <v>-0.0232016417953345</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.00844918930199145</v>
+        <v>0.10029056827084</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0787702431887468</v>
+        <v>-0.63488960520175</v>
       </c>
       <c r="AD13" t="n">
-        <v>-1.00597391700373</v>
+        <v>0.129596173698853</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.106283656636885</v>
+        <v>-0.000346176039425618</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.00766912616040909</v>
+        <v>-8.88016008611467</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.168100900357843</v>
+        <v>10.5718083691601</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.459503887674287</v>
+        <v>-10.3132268136898</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.0250448025344822</v>
+        <v>0.235458545872261</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-7.17902915184004</v>
+        <v>1.06512778425032</v>
       </c>
       <c r="AK13" t="n">
-        <v>10.1865167771572</v>
+        <v>1.04478329645459</v>
       </c>
       <c r="AL13" t="n">
-        <v>-10.7736110637694</v>
+        <v>1.2436250193625</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.00620332049695735</v>
+        <v>1.07400427593327</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.000533034160715473</v>
+        <v>0.837274531912688</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0331533520876104</v>
+        <v>1.8697104870729</v>
       </c>
       <c r="AP13" t="n">
-        <v>-3.34109907813714</v>
+        <v>-0.0232016417953345</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.23599442052073</v>
+        <v>-3.68921628388639</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.534369682602237</v>
+        <v>2.44971914892797</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.292532026701743</v>
+        <v>-0.698329443036231</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0.0203627397581943</v>
+        <v>-0.587401204304756</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.65556791314766</v>
+        <v>-0.0188036401462926</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.015700661104623</v>
+        <v>-10.837588555778</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.211132047870954</v>
+        <v>0.00225125486015426</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.02954372570078</v>
+        <v>-0.0232016417953345</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01036569933982</v>
+        <v>0.213124797157149</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.19071180505152</v>
+        <v>0.0235017043321414</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01048983671497</v>
+        <v>-0.0127727968714012</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.78974438478805</v>
+        <v>0.0412324619215205</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.79948988601498</v>
+        <v>-0.0110129494685375</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.148420789500691</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0.513037522362324</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.0383301540948154</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.00934096752396569</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.00115267060212793</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0.0459642948242026</v>
       </c>
     </row>
   </sheetData>

--- a/sum.var_AMR_ville_FQ_R.xlsx
+++ b/sum.var_AMR_ville_FQ_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prescri_1</t>
   </si>
   <si>
     <t xml:space="preserve">AMR_animaux_compagnie_C3G_R</t>
@@ -743,10 +746,13 @@
       <c r="BI1" t="s">
         <v>60</v>
       </c>
+      <c r="BJ1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" t="n">
         <v>0.00772960052286772</v>
@@ -809,129 +815,132 @@
         <v>-0.114851315499916</v>
       </c>
       <c r="V2" t="n">
+        <v>0.0783652775785313</v>
+      </c>
+      <c r="W2" t="n">
         <v>-0.00704050577408892</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>-0.00588658969639042</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>-0.0057397080210425</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>-0.0117322731793835</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>-0.0332588684908322</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>0.00772960052286772</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.154001140422901</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>0.0582695830019245</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.160323399740883</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>-0.0133806984731499</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>-12.3303494649166</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>-4.38486917941033</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>-18.8678731402826</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>0.130610908822835</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>0.375555392934203</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>0.357498405731887</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>0.152621661124171</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>-0.346688833462624</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>0.235349613528001</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>-0.209548982113039</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>0.00772960052286772</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>2.46131616730103</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>-2.19227167052624</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>-0.14689466098425</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>0.464358721866095</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
         <v>0.0193427664342699</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>11.0218902694913</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
         <v>-0.0193912798365033</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>0.00772960052286772</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="AZ2" t="n">
         <v>-0.0976156339794002</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
         <v>0.0231009862779099</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>0.0711842396775379</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>0.0133997267485429</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>-0.0116735390973381</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>-0.23814057256977</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>0.102157056829545</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>-0.0148335863570865</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
         <v>0.00535566593062078</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BI2" t="n">
         <v>0.00172099403356767</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>-0.073997723673461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" t="n">
         <v>-0.0221341414530939</v>
@@ -994,129 +1003,132 @@
         <v>0.0175382891813646</v>
       </c>
       <c r="V3" t="n">
+        <v>-0.0332510477570974</v>
+      </c>
+      <c r="W3" t="n">
         <v>-0.0217683700198446</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>-0.025007528571517</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>-0.00594697343484887</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>0.00718843060368204</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>0.0791304082566166</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>-0.0221341414530939</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>-0.0271665153679097</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>-0.770302815554919</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>0.00687099960299616</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>0.034725840262175</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>3.17771325978908</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>9.45590659332335</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>15.5290344904718</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>0.0786333169234391</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>0.44603511539236</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>0.420761142313532</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>0.117825175411432</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>-0.603686124644861</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>0.323806812980551</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>-0.671327616035061</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>-0.0221341414530939</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>-1.78849019467855</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>0.594774917323201</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>-1.71738724827605</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>-0.472378788154204</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>0.0154628528350774</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>-5.42457052529447</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>-0.010042058696367</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>-0.0221341414530939</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
         <v>-0.0689272219917101</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BA3" t="n">
         <v>-0.00596079190927153</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BB3" t="n">
         <v>-0.124494038406793</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
         <v>0.0396977072599543</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BD3" t="n">
         <v>-0.00299484608859408</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BE3" t="n">
         <v>-0.0900985847101783</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BF3" t="n">
         <v>-0.430405702605618</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BG3" t="n">
         <v>0.00420126331280438</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BH3" t="n">
         <v>-0.00686645883417283</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BI3" t="n">
         <v>-0.00212758389752027</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BJ3" t="n">
         <v>-0.733223676197547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" t="n">
         <v>-0.0203743776103109</v>
@@ -1179,129 +1191,132 @@
         <v>-0.0732747438842462</v>
       </c>
       <c r="V4" t="n">
+        <v>0.114914367516149</v>
+      </c>
+      <c r="W4" t="n">
         <v>-0.00278835022062918</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>-0.0166067860871565</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>-0.00184761400226204</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>-0.0100046443402444</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>-0.0963687065038142</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>-0.0203743776103109</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>0.238507466780687</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>-0.0055179876751338</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>0.265749097758507</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>-0.0322109025191484</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>-3.63618198377684</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>3.19198075695889</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>12.7284237561243</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>0.282585669768487</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>1.08459192358979</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>1.08405563486571</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>1.69130769280195</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>2.74556373901538</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>0.75630921144054</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>2.08339580005781</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>-0.0203743776103109</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>-4.31875399729239</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>3.56540005694909</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>-0.782589675263861</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>-1.41801144666476</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>-0.012636845194835</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>-42.063917768553</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>-0.0170909351015783</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>-0.0203743776103109</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>0.391618492627779</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BA4" t="n">
         <v>0.0545735720995601</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BB4" t="n">
         <v>-0.0654341902052057</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
         <v>0.0180099487089462</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BD4" t="n">
         <v>-0.017640294352863</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BE4" t="n">
         <v>0.271938752196663</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BF4" t="n">
         <v>0.0988875903309765</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BG4" t="n">
         <v>-0.000651213151715339</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BH4" t="n">
         <v>-0.00273756632938549</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BI4" t="n">
         <v>-0.00197807540185887</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BJ4" t="n">
         <v>-0.00507901594179504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B5" t="n">
         <v>-0.0325286853506883</v>
@@ -1364,129 +1379,132 @@
         <v>-0.0662767394077226</v>
       </c>
       <c r="V5" t="n">
+        <v>0.0296737136920025</v>
+      </c>
+      <c r="W5" t="n">
         <v>-0.0175848898050814</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>-0.0471718472427118</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>0.0108436371775343</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>0.0064511956297064</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>-0.000922632744525248</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>-0.0325286853506883</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>-0.240200751296639</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>-0.602380310114915</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>-0.239853211250507</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>0.034137452496366</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>12.8592769993275</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>-0.192251643736603</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>26.77912495624</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>-0.197700988707845</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>-0.480525696225354</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>-0.491243416945087</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>-0.517661915067306</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>-0.268031660005875</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>-0.416594915570839</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>-0.311494422645666</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>-0.0325286853506883</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>-3.27804295023073</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>0.103643179064499</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>-1.31587084830012</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>-0.38010878600959</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>-0.00859639314104966</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>-6.61747476724499</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>-0.00238507996928706</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>-0.0325286853506883</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
         <v>-0.0623337941018985</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BA5" t="n">
         <v>-0.0139735040891263</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BB5" t="n">
         <v>-0.0889789398903094</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
         <v>0.0267904630273537</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BD5" t="n">
         <v>0.000275088542728966</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BE5" t="n">
         <v>-0.498774154428945</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BF5" t="n">
         <v>-0.805735820374807</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BG5" t="n">
         <v>-0.00761274426643998</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BH5" t="n">
         <v>0.0000407778520189205</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BI5" t="n">
         <v>-0.000485969982432017</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BJ5" t="n">
         <v>-0.622655757258443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" t="n">
         <v>0.0111896546494327</v>
@@ -1549,129 +1567,132 @@
         <v>0.0248295369766438</v>
       </c>
       <c r="V6" t="n">
+        <v>-0.0694984089622275</v>
+      </c>
+      <c r="W6" t="n">
         <v>-0.0202219764604383</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>-0.015961298438483</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>0.0145774880585199</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>-0.000123590283420022</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>0.0597279019483435</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AB6" t="n">
         <v>0.0111896546494327</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>-0.0748923204047765</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>-0.423678741868557</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AE6" t="n">
         <v>-0.0594431157486579</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AF6" t="n">
         <v>-0.00900767875704805</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>-2.61132807038946</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>-6.89076795398724</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
         <v>-29.9470519040486</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
         <v>-0.0332608460612143</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>0.137839947010808</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
         <v>0.13637941094463</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>-0.122399969203203</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>-0.388364951192247</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>-0.0224633016088872</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>-0.595670602562299</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>0.0111896546494327</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>0.647163158559724</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>-3.1904011933925</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>-0.453595963951475</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>0.622946781722748</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>-0.00569921810945458</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>-15.8994468340273</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>0.00309005947437109</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AY6" t="n">
         <v>0.0111896546494327</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>-0.0650535239568293</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
         <v>-0.014554793648164</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
         <v>-0.0879917342022967</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
         <v>0.0198687079575747</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BD6" t="n">
         <v>0.00822729452788746</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BE6" t="n">
         <v>0.0877323322809686</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BF6" t="n">
         <v>-0.190653634970529</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BG6" t="n">
         <v>0.01883440585126</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BH6" t="n">
         <v>-0.00503272571077103</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BI6" t="n">
         <v>-0.000799265942887367</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BJ6" t="n">
         <v>-0.242091355144987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" t="n">
         <v>0.0016916141435206</v>
@@ -1734,129 +1755,132 @@
         <v>0.111511245163811</v>
       </c>
       <c r="V7" t="n">
+        <v>0.0276913164771287</v>
+      </c>
+      <c r="W7" t="n">
         <v>-0.000156771078757567</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>-0.000460941522093797</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>-0.000652098137484839</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>-0.0064557992462484</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>0.117467098864332</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
         <v>0.0016916141435206</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>-0.283628703906132</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>0.138826687668009</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AE7" t="n">
         <v>-0.309927730022684</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AF7" t="n">
         <v>-0.00113082445223893</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>-4.93482380993126</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>-7.22063560926808</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>19.8455533951558</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
         <v>-0.0180925555466997</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>0.418246721515095</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AL7" t="n">
         <v>0.424361583032095</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AM7" t="n">
         <v>0.289059744010996</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>0.308994584925497</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>0.159101834134017</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>0.197995368697023</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>0.0016916141435206</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>1.12134033295021</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>-5.94298722785559</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>2.15545868450043</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>1.54602068082667</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>-0.00839102625197632</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>-32.1995523411849</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>0.0131038302273313</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>0.0016916141435206</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
         <v>-0.170172304400208</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BA7" t="n">
         <v>-0.0484867898515297</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>-0.130900303696153</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BC7" t="n">
         <v>-0.0097474141827183</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BD7" t="n">
         <v>0.0262124964709996</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BE7" t="n">
         <v>0.357638558366775</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BF7" t="n">
         <v>-0.563513299647262</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BG7" t="n">
         <v>0.018776500720234</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BH7" t="n">
         <v>0.0165749855340629</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BI7" t="n">
         <v>0.00341200918641746</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BJ7" t="n">
         <v>0.420820327277151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" t="n">
         <v>0.0237992005741522</v>
@@ -1919,129 +1943,132 @@
         <v>0.0918117366690664</v>
       </c>
       <c r="V8" t="n">
+        <v>0.00189803511554691</v>
+      </c>
+      <c r="W8" t="n">
         <v>0.0317868662453055</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>0.0433669709025216</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-0.00203471874096844</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>-0.00704514598014381</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-0.0612103131719041</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AB8" t="n">
         <v>0.0237992005741522</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>-0.0196716387334885</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>1.71905337412741</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AE8" t="n">
         <v>-0.0529446881570243</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AF8" t="n">
         <v>0.0328225723340265</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>-9.01272307721351</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>-16.3377612856515</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>-92.0387708878531</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
         <v>-0.324050522133134</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>-1.96214937859133</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>-1.89546618886632</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>-1.89651190208578</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>-1.22021097105653</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>-1.22631695627796</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>-0.810419476847576</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>0.0237992005741522</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>11.0611048510848</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>-8.13657157043532</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>1.89965622981696</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>1.2231669853248</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>-0.00797225887403143</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>-14.3772288344109</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>0.0976463849176611</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
         <v>0.0237992005741522</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
         <v>-0.160721921099835</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BA8" t="n">
         <v>0.00718328310658834</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
         <v>0.623368914024887</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BC8" t="n">
         <v>-0.104572526869896</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BD8" t="n">
         <v>-0.00235061950876203</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BE8" t="n">
         <v>-0.364227869492569</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BF8" t="n">
         <v>0.868083983240932</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BG8" t="n">
         <v>-0.0457772676852642</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BH8" t="n">
         <v>0.0175497742443751</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BI8" t="n">
         <v>0.00697314120095147</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BJ8" t="n">
         <v>2.10000862327134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B9" t="n">
         <v>-0.0107601668485331</v>
@@ -2104,129 +2131,132 @@
         <v>0.0416848994848347</v>
       </c>
       <c r="V9" t="n">
+        <v>0.0247461477456109</v>
+      </c>
+      <c r="W9" t="n">
         <v>-0.00113998729489261</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.016912909640061</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>-0.000969293831558328</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>-0.00545927080555194</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>-0.0674828256708319</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AB9" t="n">
         <v>-0.0107601668485331</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>0.120325299563882</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>-0.314908419026853</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AE9" t="n">
         <v>0.0986064075879345</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
         <v>-0.0568021735079</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>-0.624784079803963</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>24.7971160064304</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>21.1224527119021</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>0.229753807778225</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>1.05828541957378</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AL9" t="n">
         <v>1.06438261422827</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>0.785942009562261</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>0.487882730365099</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>0.697195612240213</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>-0.0374455911788562</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>-0.0107601668485331</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>-1.67028852900829</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>-0.0109312412913779</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>-0.191921675231057</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>-0.336248048840461</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>-0.0114423256380421</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>-38.3424138223202</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>-0.0208097444155831</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
         <v>-0.0107601668485331</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
         <v>0.074872943332801</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BA9" t="n">
         <v>-0.0309050695110712</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BB9" t="n">
         <v>-0.085804112752481</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BC9" t="n">
         <v>0.0321586612015137</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BD9" t="n">
         <v>0.00173258813346108</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BE9" t="n">
         <v>-0.0206447053958451</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BF9" t="n">
         <v>-0.56047013214129</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BG9" t="n">
         <v>-0.000343998372898837</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BH9" t="n">
         <v>0.00197200880993254</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BI9" t="n">
         <v>-0.000229650166180577</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BJ9" t="n">
         <v>-0.10211662579286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" t="n">
         <v>0.00379607876635765</v>
@@ -2289,129 +2319,132 @@
         <v>0.0274333514639498</v>
       </c>
       <c r="V10" t="n">
+        <v>-0.0338589119520969</v>
+      </c>
+      <c r="W10" t="n">
         <v>-0.00351881208243151</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>-0.00206017283480927</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>-0.00540575234929896</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>-0.00579879783185996</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>0.000139235351569367</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AB10" t="n">
         <v>0.00379607876635765</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>-0.0342589796517672</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>-0.317730159419209</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
         <v>-0.0346914560561887</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AF10" t="n">
         <v>0.00300079312805353</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>9.18564175834393</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>2.60351806295416</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>38.9228280039465</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>-0.0079908077062404</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>0.0993371854900619</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>0.0648298521035288</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>0.120572232824682</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
         <v>-0.117960350491315</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>0.0824821535077846</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>0.322043412432475</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>0.00379607876635765</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>-3.36054905774655</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>0.125640023711585</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>-1.05862112080309</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>-0.969569942067806</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>-0.00465036666388241</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>20.4716391934634</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>-0.00852965206021429</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AY10" t="n">
         <v>0.00379607876635765</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
         <v>0.123513363905274</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BA10" t="n">
         <v>0.0165868695718829</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
         <v>-0.0682606175468987</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
         <v>0.00640762906621618</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BD10" t="n">
         <v>-0.00231622520835979</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BE10" t="n">
         <v>0.226721715917034</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BF10" t="n">
         <v>0.255688366175892</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BG10" t="n">
         <v>0.00678206785536286</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BH10" t="n">
         <v>-0.01638452748375</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BI10" t="n">
         <v>-0.00423125097371813</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BJ10" t="n">
         <v>-0.544121789461287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" t="n">
         <v>0.00330590970407478</v>
@@ -2474,129 +2507,132 @@
         <v>0.0233233898465209</v>
       </c>
       <c r="V11" t="n">
+        <v>-0.134269002145114</v>
+      </c>
+      <c r="W11" t="n">
         <v>-0.0160402896903781</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.0257710771195284</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.0169332582755317</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>0.0533113040488226</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>0.1346138312419</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
         <v>0.00330590970407478</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>-0.0354567410752362</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>0.128949509529747</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>-0.0422757744771231</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>-0.0174550436587456</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>6.42513956495643</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>-3.78655200623572</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>28.9449742236903</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>-0.0951203534760066</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>-0.280465339930393</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>-0.315517269456471</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
         <v>-0.268724626977033</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>-0.489446482450284</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>-0.198475120765655</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>-0.48313178901756</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>0.00330590970407478</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>-1.42640909208072</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>5.91211095973774</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>-0.895613718645758</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>-0.823422918814776</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>0.0198046521585685</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>64.7608500031866</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>0.00442311960733503</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>0.00330590970407478</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AZ11" t="n">
         <v>0.0725586485713087</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BA11" t="n">
         <v>0.00457331816569248</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BB11" t="n">
         <v>-0.0794686588701281</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BC11" t="n">
         <v>-0.022730959003571</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BD11" t="n">
         <v>0.00562799823828984</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BE11" t="n">
         <v>0.132832947960337</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BF11" t="n">
         <v>0.482211586012499</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BG11" t="n">
         <v>0.0253117043650773</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BH11" t="n">
         <v>-0.0103886763340441</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BI11" t="n">
         <v>-0.00230109366776357</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BJ11" t="n">
         <v>-0.416902965091475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B12" t="n">
         <v>0.0574869546975551</v>
@@ -2659,129 +2695,132 @@
         <v>0.0855989607660336</v>
       </c>
       <c r="V12" t="n">
+        <v>-0.193983119750397</v>
+      </c>
+      <c r="W12" t="n">
         <v>0.0325476245037432</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0.0342387392245079</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>-0.0158690518044377</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>-0.00954756689330399</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>-0.0634160524993205</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AB12" t="n">
         <v>0.0574869546975551</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>0.10215117539764</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>1.02430888453424</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AE12" t="n">
         <v>0.0779898973230106</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AF12" t="n">
         <v>0.0256468391870354</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>10.3825789897294</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>-11.8074921105374</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>-12.7054687916566</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>-0.280826175534107</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AK12" t="n">
         <v>-1.96187907500934</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AL12" t="n">
         <v>-1.89482506440636</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>-1.59565512176468</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>-1.18205595693551</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>-1.22766947552045</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>-1.35410658786014</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>0.0574869546975551</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>4.24082559502784</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>6.72187461778694</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>3.20570944017448</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>1.13064796511604</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>0.0235818025916482</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>69.5078139826724</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>-0.0422658990073197</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>0.0574869546975551</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
         <v>-0.25086384606443</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BA12" t="n">
         <v>-0.0156387845446128</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
         <v>0.0495522387392417</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BC12" t="n">
         <v>-0.0605144058354366</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BD12" t="n">
         <v>0.0059130078110877</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BE12" t="n">
         <v>0.283442369376223</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BF12" t="n">
         <v>1.25678752951199</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BG12" t="n">
         <v>0.0336430218234816</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BH12" t="n">
         <v>-0.00942422520285237</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BI12" t="n">
         <v>-0.00110592499070373</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BJ12" t="n">
         <v>0.265324252837569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" t="n">
         <v>-0.0232016417953345</v>
@@ -2844,123 +2883,126 @@
         <v>-0.16932861076034</v>
       </c>
       <c r="V13" t="n">
+        <v>0.187571632441963</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.0259254616774935</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>-0.00713453249345702</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>-0.00388917318968417</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>-0.010783841722055</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>-0.0684190765815336</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
         <v>-0.0232016417953345</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>0.10029056827084</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>-0.63488960520175</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AE13" t="n">
         <v>0.129596173698853</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AF13" t="n">
         <v>-0.000346176039425618</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>-8.88016008611467</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>10.5718083691601</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>-10.3132268136898</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>0.235458545872261</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
         <v>1.06512778425032</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>1.04478329645459</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AM13" t="n">
         <v>1.2436250193625</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
         <v>1.07400427593327</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>0.837274531912688</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>1.8697104870729</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>-0.0232016417953345</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>-3.68921628388639</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>2.44971914892797</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>-0.698329443036231</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>-0.587401204304756</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>-0.0188036401462926</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>-10.837588555778</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>0.00225125486015426</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
         <v>-0.0232016417953345</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
         <v>0.213124797157149</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BA13" t="n">
         <v>0.0235017043321414</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BB13" t="n">
         <v>-0.0127727968714012</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BC13" t="n">
         <v>0.0412324619215205</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
         <v>-0.0110129494685375</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
         <v>-0.148420789500691</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BF13" t="n">
         <v>-0.513037522362324</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BG13" t="n">
         <v>-0.0383301540948154</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BH13" t="n">
         <v>0.00934096752396569</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BI13" t="n">
         <v>0.00115267060212793</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BJ13" t="n">
         <v>-0.0459642948242026</v>
       </c>
     </row>
